--- a/files/temp_files/statement_2025_02.xlsx
+++ b/files/temp_files/statement_2025_02.xlsx
@@ -588,7 +588,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>2.03</v>
+        <v>-2.03</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -616,7 +616,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>558.15</v>
+        <v>-558.15</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -630,7 +630,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>166.87</v>
+        <v>-166.87</v>
       </c>
       <c r="D5" t="s">
         <v>58</v>
@@ -644,7 +644,7 @@
         <v>36</v>
       </c>
       <c r="C6">
-        <v>32.92</v>
+        <v>-32.92</v>
       </c>
       <c r="D6" t="s">
         <v>59</v>
@@ -658,7 +658,7 @@
         <v>37</v>
       </c>
       <c r="C7">
-        <v>33.54</v>
+        <v>-33.54</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -672,7 +672,7 @@
         <v>38</v>
       </c>
       <c r="C8">
-        <v>152.35</v>
+        <v>-152.35</v>
       </c>
       <c r="D8" t="s">
         <v>61</v>
@@ -686,7 +686,7 @@
         <v>39</v>
       </c>
       <c r="C9">
-        <v>86.76000000000001</v>
+        <v>-86.76000000000001</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -700,7 +700,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>78.52</v>
+        <v>-78.52</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
@@ -714,7 +714,7 @@
         <v>35</v>
       </c>
       <c r="C11">
-        <v>46.85</v>
+        <v>-46.85</v>
       </c>
       <c r="D11" t="s">
         <v>58</v>
@@ -728,7 +728,7 @@
         <v>39</v>
       </c>
       <c r="C12">
-        <v>209.64</v>
+        <v>-209.64</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
@@ -742,7 +742,7 @@
         <v>40</v>
       </c>
       <c r="C13">
-        <v>80.23</v>
+        <v>-80.23</v>
       </c>
       <c r="D13" t="s">
         <v>58</v>
@@ -756,7 +756,7 @@
         <v>41</v>
       </c>
       <c r="C14">
-        <v>80.44</v>
+        <v>-80.44</v>
       </c>
       <c r="D14" t="s">
         <v>60</v>
@@ -770,7 +770,7 @@
         <v>42</v>
       </c>
       <c r="C15">
-        <v>82.23999999999999</v>
+        <v>-82.23999999999999</v>
       </c>
       <c r="D15" t="s">
         <v>62</v>
@@ -784,7 +784,7 @@
         <v>43</v>
       </c>
       <c r="C16">
-        <v>195.91</v>
+        <v>-195.91</v>
       </c>
       <c r="D16" t="s">
         <v>59</v>
@@ -798,7 +798,7 @@
         <v>43</v>
       </c>
       <c r="C17">
-        <v>61.72</v>
+        <v>-61.72</v>
       </c>
       <c r="D17" t="s">
         <v>59</v>
@@ -812,7 +812,7 @@
         <v>44</v>
       </c>
       <c r="C18">
-        <v>415.04</v>
+        <v>-415.04</v>
       </c>
       <c r="D18" t="s">
         <v>61</v>
@@ -826,7 +826,7 @@
         <v>45</v>
       </c>
       <c r="C19">
-        <v>82.61</v>
+        <v>-82.61</v>
       </c>
       <c r="D19" t="s">
         <v>58</v>
@@ -854,7 +854,7 @@
         <v>47</v>
       </c>
       <c r="C21">
-        <v>12.68</v>
+        <v>-12.68</v>
       </c>
       <c r="D21" t="s">
         <v>63</v>
@@ -868,7 +868,7 @@
         <v>36</v>
       </c>
       <c r="C22">
-        <v>199.84</v>
+        <v>-199.84</v>
       </c>
       <c r="D22" t="s">
         <v>59</v>
@@ -882,7 +882,7 @@
         <v>40</v>
       </c>
       <c r="C23">
-        <v>78.28</v>
+        <v>-78.28</v>
       </c>
       <c r="D23" t="s">
         <v>58</v>
@@ -910,7 +910,7 @@
         <v>36</v>
       </c>
       <c r="C25">
-        <v>66.45999999999999</v>
+        <v>-66.45999999999999</v>
       </c>
       <c r="D25" t="s">
         <v>59</v>
@@ -924,7 +924,7 @@
         <v>39</v>
       </c>
       <c r="C26">
-        <v>74.83</v>
+        <v>-74.83</v>
       </c>
       <c r="D26" t="s">
         <v>56</v>
@@ -938,7 +938,7 @@
         <v>48</v>
       </c>
       <c r="C27">
-        <v>133.62</v>
+        <v>-133.62</v>
       </c>
       <c r="D27" t="s">
         <v>60</v>
@@ -952,7 +952,7 @@
         <v>36</v>
       </c>
       <c r="C28">
-        <v>143.11</v>
+        <v>-143.11</v>
       </c>
       <c r="D28" t="s">
         <v>59</v>
@@ -966,7 +966,7 @@
         <v>42</v>
       </c>
       <c r="C29">
-        <v>34.03</v>
+        <v>-34.03</v>
       </c>
       <c r="D29" t="s">
         <v>62</v>
@@ -980,7 +980,7 @@
         <v>37</v>
       </c>
       <c r="C30">
-        <v>79.72</v>
+        <v>-79.72</v>
       </c>
       <c r="D30" t="s">
         <v>60</v>
@@ -994,7 +994,7 @@
         <v>34</v>
       </c>
       <c r="C31">
-        <v>495.13</v>
+        <v>-495.13</v>
       </c>
       <c r="D31" t="s">
         <v>56</v>
@@ -1008,7 +1008,7 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>44.68</v>
+        <v>-44.68</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1022,7 +1022,7 @@
         <v>36</v>
       </c>
       <c r="C33">
-        <v>187.25</v>
+        <v>-187.25</v>
       </c>
       <c r="D33" t="s">
         <v>59</v>
@@ -1036,7 +1036,7 @@
         <v>37</v>
       </c>
       <c r="C34">
-        <v>135.77</v>
+        <v>-135.77</v>
       </c>
       <c r="D34" t="s">
         <v>60</v>
@@ -1050,7 +1050,7 @@
         <v>32</v>
       </c>
       <c r="C35">
-        <v>793.5</v>
+        <v>-793.5</v>
       </c>
       <c r="D35" t="s">
         <v>56</v>
@@ -1078,7 +1078,7 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>15.03</v>
+        <v>-15.03</v>
       </c>
       <c r="D37" t="s">
         <v>56</v>
@@ -1092,7 +1092,7 @@
         <v>34</v>
       </c>
       <c r="C38">
-        <v>137.62</v>
+        <v>-137.62</v>
       </c>
       <c r="D38" t="s">
         <v>56</v>
@@ -1106,7 +1106,7 @@
         <v>32</v>
       </c>
       <c r="C39">
-        <v>18.49</v>
+        <v>-18.49</v>
       </c>
       <c r="D39" t="s">
         <v>56</v>
@@ -1120,7 +1120,7 @@
         <v>49</v>
       </c>
       <c r="C40">
-        <v>58.82</v>
+        <v>-58.82</v>
       </c>
       <c r="D40" t="s">
         <v>59</v>
@@ -1134,7 +1134,7 @@
         <v>47</v>
       </c>
       <c r="C41">
-        <v>26.28</v>
+        <v>-26.28</v>
       </c>
       <c r="D41" t="s">
         <v>63</v>
@@ -1148,7 +1148,7 @@
         <v>38</v>
       </c>
       <c r="C42">
-        <v>309.42</v>
+        <v>-309.42</v>
       </c>
       <c r="D42" t="s">
         <v>61</v>
@@ -1162,7 +1162,7 @@
         <v>47</v>
       </c>
       <c r="C43">
-        <v>41.33</v>
+        <v>-41.33</v>
       </c>
       <c r="D43" t="s">
         <v>63</v>
@@ -1176,7 +1176,7 @@
         <v>38</v>
       </c>
       <c r="C44">
-        <v>48.52</v>
+        <v>-48.52</v>
       </c>
       <c r="D44" t="s">
         <v>61</v>
@@ -1190,7 +1190,7 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>25.01</v>
+        <v>-25.01</v>
       </c>
       <c r="D45" t="s">
         <v>63</v>
@@ -1204,7 +1204,7 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>37.02</v>
+        <v>-37.02</v>
       </c>
       <c r="D46" t="s">
         <v>62</v>
@@ -1218,7 +1218,7 @@
         <v>48</v>
       </c>
       <c r="C47">
-        <v>85.13</v>
+        <v>-85.13</v>
       </c>
       <c r="D47" t="s">
         <v>60</v>
@@ -1232,7 +1232,7 @@
         <v>43</v>
       </c>
       <c r="C48">
-        <v>103.62</v>
+        <v>-103.62</v>
       </c>
       <c r="D48" t="s">
         <v>59</v>
@@ -1246,7 +1246,7 @@
         <v>45</v>
       </c>
       <c r="C49">
-        <v>207</v>
+        <v>-207</v>
       </c>
       <c r="D49" t="s">
         <v>58</v>
@@ -1260,7 +1260,7 @@
         <v>44</v>
       </c>
       <c r="C50">
-        <v>72</v>
+        <v>-72</v>
       </c>
       <c r="D50" t="s">
         <v>61</v>
@@ -1274,7 +1274,7 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>7.63</v>
+        <v>-7.63</v>
       </c>
       <c r="D51" t="s">
         <v>63</v>
@@ -1288,7 +1288,7 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>66.94</v>
+        <v>-66.94</v>
       </c>
       <c r="D52" t="s">
         <v>62</v>
@@ -1302,7 +1302,7 @@
         <v>47</v>
       </c>
       <c r="C53">
-        <v>12.15</v>
+        <v>-12.15</v>
       </c>
       <c r="D53" t="s">
         <v>63</v>
@@ -1316,7 +1316,7 @@
         <v>48</v>
       </c>
       <c r="C54">
-        <v>33.06</v>
+        <v>-33.06</v>
       </c>
       <c r="D54" t="s">
         <v>60</v>
@@ -1344,7 +1344,7 @@
         <v>52</v>
       </c>
       <c r="C56">
-        <v>67.56999999999999</v>
+        <v>-67.56999999999999</v>
       </c>
       <c r="D56" t="s">
         <v>62</v>
@@ -1358,7 +1358,7 @@
         <v>47</v>
       </c>
       <c r="C57">
-        <v>18.8</v>
+        <v>-18.8</v>
       </c>
       <c r="D57" t="s">
         <v>63</v>
@@ -1372,7 +1372,7 @@
         <v>32</v>
       </c>
       <c r="C58">
-        <v>370.47</v>
+        <v>-370.47</v>
       </c>
       <c r="D58" t="s">
         <v>56</v>
@@ -1386,7 +1386,7 @@
         <v>32</v>
       </c>
       <c r="C59">
-        <v>506.02</v>
+        <v>-506.02</v>
       </c>
       <c r="D59" t="s">
         <v>56</v>
@@ -1400,7 +1400,7 @@
         <v>35</v>
       </c>
       <c r="C60">
-        <v>221.19</v>
+        <v>-221.19</v>
       </c>
       <c r="D60" t="s">
         <v>58</v>
@@ -1414,7 +1414,7 @@
         <v>35</v>
       </c>
       <c r="C61">
-        <v>30.42</v>
+        <v>-30.42</v>
       </c>
       <c r="D61" t="s">
         <v>58</v>
@@ -1442,7 +1442,7 @@
         <v>51</v>
       </c>
       <c r="C63">
-        <v>64.86</v>
+        <v>-64.86</v>
       </c>
       <c r="D63" t="s">
         <v>62</v>
@@ -1456,7 +1456,7 @@
         <v>53</v>
       </c>
       <c r="C64">
-        <v>16.24</v>
+        <v>-16.24</v>
       </c>
       <c r="D64" t="s">
         <v>63</v>
@@ -1470,7 +1470,7 @@
         <v>52</v>
       </c>
       <c r="C65">
-        <v>79.69</v>
+        <v>-79.69</v>
       </c>
       <c r="D65" t="s">
         <v>62</v>
@@ -1484,7 +1484,7 @@
         <v>41</v>
       </c>
       <c r="C66">
-        <v>54.94</v>
+        <v>-54.94</v>
       </c>
       <c r="D66" t="s">
         <v>60</v>
@@ -1498,7 +1498,7 @@
         <v>50</v>
       </c>
       <c r="C67">
-        <v>35.24</v>
+        <v>-35.24</v>
       </c>
       <c r="D67" t="s">
         <v>63</v>
@@ -1512,7 +1512,7 @@
         <v>48</v>
       </c>
       <c r="C68">
-        <v>94.59</v>
+        <v>-94.59</v>
       </c>
       <c r="D68" t="s">
         <v>60</v>
@@ -1526,7 +1526,7 @@
         <v>39</v>
       </c>
       <c r="C69">
-        <v>411.79</v>
+        <v>-411.79</v>
       </c>
       <c r="D69" t="s">
         <v>56</v>
@@ -1540,7 +1540,7 @@
         <v>34</v>
       </c>
       <c r="C70">
-        <v>766.15</v>
+        <v>-766.15</v>
       </c>
       <c r="D70" t="s">
         <v>56</v>
@@ -1554,7 +1554,7 @@
         <v>34</v>
       </c>
       <c r="C71">
-        <v>358.95</v>
+        <v>-358.95</v>
       </c>
       <c r="D71" t="s">
         <v>56</v>
@@ -1568,7 +1568,7 @@
         <v>36</v>
       </c>
       <c r="C72">
-        <v>25.31</v>
+        <v>-25.31</v>
       </c>
       <c r="D72" t="s">
         <v>59</v>
@@ -1582,7 +1582,7 @@
         <v>41</v>
       </c>
       <c r="C73">
-        <v>117.36</v>
+        <v>-117.36</v>
       </c>
       <c r="D73" t="s">
         <v>60</v>
@@ -1596,7 +1596,7 @@
         <v>36</v>
       </c>
       <c r="C74">
-        <v>104.78</v>
+        <v>-104.78</v>
       </c>
       <c r="D74" t="s">
         <v>59</v>
@@ -1610,7 +1610,7 @@
         <v>34</v>
       </c>
       <c r="C75">
-        <v>461.12</v>
+        <v>-461.12</v>
       </c>
       <c r="D75" t="s">
         <v>56</v>
@@ -1624,7 +1624,7 @@
         <v>34</v>
       </c>
       <c r="C76">
-        <v>223.67</v>
+        <v>-223.67</v>
       </c>
       <c r="D76" t="s">
         <v>56</v>
@@ -1638,7 +1638,7 @@
         <v>51</v>
       </c>
       <c r="C77">
-        <v>41.75</v>
+        <v>-41.75</v>
       </c>
       <c r="D77" t="s">
         <v>62</v>
@@ -1652,7 +1652,7 @@
         <v>37</v>
       </c>
       <c r="C78">
-        <v>82.55</v>
+        <v>-82.55</v>
       </c>
       <c r="D78" t="s">
         <v>60</v>
@@ -1666,7 +1666,7 @@
         <v>43</v>
       </c>
       <c r="C79">
-        <v>80.34</v>
+        <v>-80.34</v>
       </c>
       <c r="D79" t="s">
         <v>59</v>
@@ -1680,7 +1680,7 @@
         <v>50</v>
       </c>
       <c r="C80">
-        <v>46.14</v>
+        <v>-46.14</v>
       </c>
       <c r="D80" t="s">
         <v>63</v>
@@ -1708,7 +1708,7 @@
         <v>42</v>
       </c>
       <c r="C82">
-        <v>44.4</v>
+        <v>-44.4</v>
       </c>
       <c r="D82" t="s">
         <v>62</v>
@@ -1722,7 +1722,7 @@
         <v>42</v>
       </c>
       <c r="C83">
-        <v>39.45</v>
+        <v>-39.45</v>
       </c>
       <c r="D83" t="s">
         <v>62</v>
@@ -1750,7 +1750,7 @@
         <v>44</v>
       </c>
       <c r="C85">
-        <v>153.67</v>
+        <v>-153.67</v>
       </c>
       <c r="D85" t="s">
         <v>61</v>
@@ -1764,7 +1764,7 @@
         <v>38</v>
       </c>
       <c r="C86">
-        <v>58.92</v>
+        <v>-58.92</v>
       </c>
       <c r="D86" t="s">
         <v>61</v>
@@ -1792,7 +1792,7 @@
         <v>45</v>
       </c>
       <c r="C88">
-        <v>56.69</v>
+        <v>-56.69</v>
       </c>
       <c r="D88" t="s">
         <v>58</v>
@@ -1806,7 +1806,7 @@
         <v>37</v>
       </c>
       <c r="C89">
-        <v>142.29</v>
+        <v>-142.29</v>
       </c>
       <c r="D89" t="s">
         <v>60</v>
@@ -1820,7 +1820,7 @@
         <v>42</v>
       </c>
       <c r="C90">
-        <v>54.75</v>
+        <v>-54.75</v>
       </c>
       <c r="D90" t="s">
         <v>62</v>
@@ -1834,7 +1834,7 @@
         <v>38</v>
       </c>
       <c r="C91">
-        <v>170.17</v>
+        <v>-170.17</v>
       </c>
       <c r="D91" t="s">
         <v>61</v>
@@ -1848,7 +1848,7 @@
         <v>50</v>
       </c>
       <c r="C92">
-        <v>47.2</v>
+        <v>-47.2</v>
       </c>
       <c r="D92" t="s">
         <v>63</v>
@@ -1862,7 +1862,7 @@
         <v>34</v>
       </c>
       <c r="C93">
-        <v>979.6799999999999</v>
+        <v>-979.6799999999999</v>
       </c>
       <c r="D93" t="s">
         <v>56</v>
@@ -1876,7 +1876,7 @@
         <v>52</v>
       </c>
       <c r="C94">
-        <v>68.26000000000001</v>
+        <v>-68.26000000000001</v>
       </c>
       <c r="D94" t="s">
         <v>62</v>
@@ -1890,7 +1890,7 @@
         <v>39</v>
       </c>
       <c r="C95">
-        <v>926.04</v>
+        <v>-926.04</v>
       </c>
       <c r="D95" t="s">
         <v>56</v>
@@ -1904,7 +1904,7 @@
         <v>37</v>
       </c>
       <c r="C96">
-        <v>63.87</v>
+        <v>-63.87</v>
       </c>
       <c r="D96" t="s">
         <v>60</v>
@@ -1918,7 +1918,7 @@
         <v>42</v>
       </c>
       <c r="C97">
-        <v>71.58</v>
+        <v>-71.58</v>
       </c>
       <c r="D97" t="s">
         <v>62</v>
@@ -1932,7 +1932,7 @@
         <v>50</v>
       </c>
       <c r="C98">
-        <v>47.02</v>
+        <v>-47.02</v>
       </c>
       <c r="D98" t="s">
         <v>63</v>
@@ -1946,7 +1946,7 @@
         <v>34</v>
       </c>
       <c r="C99">
-        <v>320.59</v>
+        <v>-320.59</v>
       </c>
       <c r="D99" t="s">
         <v>56</v>
@@ -1960,7 +1960,7 @@
         <v>48</v>
       </c>
       <c r="C100">
-        <v>48.26</v>
+        <v>-48.26</v>
       </c>
       <c r="D100" t="s">
         <v>60</v>
@@ -2002,7 +2002,7 @@
         <v>41</v>
       </c>
       <c r="C103">
-        <v>35.3</v>
+        <v>-35.3</v>
       </c>
       <c r="D103" t="s">
         <v>60</v>
@@ -2030,7 +2030,7 @@
         <v>43</v>
       </c>
       <c r="C105">
-        <v>21.45</v>
+        <v>-21.45</v>
       </c>
       <c r="D105" t="s">
         <v>59</v>
@@ -2044,7 +2044,7 @@
         <v>41</v>
       </c>
       <c r="C106">
-        <v>105.84</v>
+        <v>-105.84</v>
       </c>
       <c r="D106" t="s">
         <v>60</v>
@@ -2058,7 +2058,7 @@
         <v>49</v>
       </c>
       <c r="C107">
-        <v>179.81</v>
+        <v>-179.81</v>
       </c>
       <c r="D107" t="s">
         <v>59</v>
@@ -2072,7 +2072,7 @@
         <v>55</v>
       </c>
       <c r="C108">
-        <v>452.1</v>
+        <v>-452.1</v>
       </c>
       <c r="D108" t="s">
         <v>61</v>
@@ -2086,7 +2086,7 @@
         <v>52</v>
       </c>
       <c r="C109">
-        <v>10.71</v>
+        <v>-10.71</v>
       </c>
       <c r="D109" t="s">
         <v>62</v>
@@ -2100,7 +2100,7 @@
         <v>49</v>
       </c>
       <c r="C110">
-        <v>195.81</v>
+        <v>-195.81</v>
       </c>
       <c r="D110" t="s">
         <v>59</v>
@@ -2128,7 +2128,7 @@
         <v>38</v>
       </c>
       <c r="C112">
-        <v>458.81</v>
+        <v>-458.81</v>
       </c>
       <c r="D112" t="s">
         <v>61</v>
@@ -2156,7 +2156,7 @@
         <v>47</v>
       </c>
       <c r="C114">
-        <v>20.55</v>
+        <v>-20.55</v>
       </c>
       <c r="D114" t="s">
         <v>63</v>
@@ -2170,7 +2170,7 @@
         <v>49</v>
       </c>
       <c r="C115">
-        <v>137.95</v>
+        <v>-137.95</v>
       </c>
       <c r="D115" t="s">
         <v>59</v>
@@ -2184,7 +2184,7 @@
         <v>50</v>
       </c>
       <c r="C116">
-        <v>25.62</v>
+        <v>-25.62</v>
       </c>
       <c r="D116" t="s">
         <v>63</v>
@@ -2198,7 +2198,7 @@
         <v>32</v>
       </c>
       <c r="C117">
-        <v>615.49</v>
+        <v>-615.49</v>
       </c>
       <c r="D117" t="s">
         <v>56</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="C119">
-        <v>894.13</v>
+        <v>-894.13</v>
       </c>
       <c r="D119" t="s">
         <v>56</v>
@@ -2240,7 +2240,7 @@
         <v>35</v>
       </c>
       <c r="C120">
-        <v>213.62</v>
+        <v>-213.62</v>
       </c>
       <c r="D120" t="s">
         <v>58</v>
@@ -2268,7 +2268,7 @@
         <v>40</v>
       </c>
       <c r="C122">
-        <v>76.19</v>
+        <v>-76.19</v>
       </c>
       <c r="D122" t="s">
         <v>58</v>
@@ -2282,7 +2282,7 @@
         <v>39</v>
       </c>
       <c r="C123">
-        <v>555.05</v>
+        <v>-555.05</v>
       </c>
       <c r="D123" t="s">
         <v>56</v>
@@ -2296,7 +2296,7 @@
         <v>53</v>
       </c>
       <c r="C124">
-        <v>15.8</v>
+        <v>-15.8</v>
       </c>
       <c r="D124" t="s">
         <v>63</v>
@@ -2310,7 +2310,7 @@
         <v>49</v>
       </c>
       <c r="C125">
-        <v>48.7</v>
+        <v>-48.7</v>
       </c>
       <c r="D125" t="s">
         <v>59</v>
@@ -2324,7 +2324,7 @@
         <v>48</v>
       </c>
       <c r="C126">
-        <v>40.76</v>
+        <v>-40.76</v>
       </c>
       <c r="D126" t="s">
         <v>60</v>
@@ -2338,7 +2338,7 @@
         <v>34</v>
       </c>
       <c r="C127">
-        <v>988.02</v>
+        <v>-988.02</v>
       </c>
       <c r="D127" t="s">
         <v>56</v>
@@ -2352,7 +2352,7 @@
         <v>48</v>
       </c>
       <c r="C128">
-        <v>85.7</v>
+        <v>-85.7</v>
       </c>
       <c r="D128" t="s">
         <v>60</v>
@@ -2366,7 +2366,7 @@
         <v>53</v>
       </c>
       <c r="C129">
-        <v>39.56</v>
+        <v>-39.56</v>
       </c>
       <c r="D129" t="s">
         <v>63</v>
@@ -2380,7 +2380,7 @@
         <v>49</v>
       </c>
       <c r="C130">
-        <v>124.26</v>
+        <v>-124.26</v>
       </c>
       <c r="D130" t="s">
         <v>59</v>
@@ -2394,7 +2394,7 @@
         <v>43</v>
       </c>
       <c r="C131">
-        <v>128.79</v>
+        <v>-128.79</v>
       </c>
       <c r="D131" t="s">
         <v>59</v>
@@ -2408,7 +2408,7 @@
         <v>37</v>
       </c>
       <c r="C132">
-        <v>76.69</v>
+        <v>-76.69</v>
       </c>
       <c r="D132" t="s">
         <v>60</v>
@@ -2436,7 +2436,7 @@
         <v>48</v>
       </c>
       <c r="C134">
-        <v>137.9</v>
+        <v>-137.9</v>
       </c>
       <c r="D134" t="s">
         <v>60</v>
@@ -2450,7 +2450,7 @@
         <v>42</v>
       </c>
       <c r="C135">
-        <v>37.52</v>
+        <v>-37.52</v>
       </c>
       <c r="D135" t="s">
         <v>62</v>
@@ -2478,7 +2478,7 @@
         <v>48</v>
       </c>
       <c r="C137">
-        <v>63.74</v>
+        <v>-63.74</v>
       </c>
       <c r="D137" t="s">
         <v>60</v>
@@ -2492,7 +2492,7 @@
         <v>39</v>
       </c>
       <c r="C138">
-        <v>925.24</v>
+        <v>-925.24</v>
       </c>
       <c r="D138" t="s">
         <v>56</v>
@@ -2506,7 +2506,7 @@
         <v>38</v>
       </c>
       <c r="C139">
-        <v>271.12</v>
+        <v>-271.12</v>
       </c>
       <c r="D139" t="s">
         <v>61</v>
@@ -2534,7 +2534,7 @@
         <v>53</v>
       </c>
       <c r="C141">
-        <v>39.06</v>
+        <v>-39.06</v>
       </c>
       <c r="D141" t="s">
         <v>63</v>
@@ -2548,7 +2548,7 @@
         <v>40</v>
       </c>
       <c r="C142">
-        <v>194.57</v>
+        <v>-194.57</v>
       </c>
       <c r="D142" t="s">
         <v>58</v>
@@ -2562,7 +2562,7 @@
         <v>55</v>
       </c>
       <c r="C143">
-        <v>283.84</v>
+        <v>-283.84</v>
       </c>
       <c r="D143" t="s">
         <v>61</v>
@@ -2576,7 +2576,7 @@
         <v>35</v>
       </c>
       <c r="C144">
-        <v>71.72</v>
+        <v>-71.72</v>
       </c>
       <c r="D144" t="s">
         <v>58</v>
@@ -2590,7 +2590,7 @@
         <v>32</v>
       </c>
       <c r="C145">
-        <v>407.39</v>
+        <v>-407.39</v>
       </c>
       <c r="D145" t="s">
         <v>56</v>
@@ -2604,7 +2604,7 @@
         <v>49</v>
       </c>
       <c r="C146">
-        <v>160.98</v>
+        <v>-160.98</v>
       </c>
       <c r="D146" t="s">
         <v>59</v>
@@ -2632,7 +2632,7 @@
         <v>50</v>
       </c>
       <c r="C148">
-        <v>10.92</v>
+        <v>-10.92</v>
       </c>
       <c r="D148" t="s">
         <v>63</v>
@@ -2646,7 +2646,7 @@
         <v>44</v>
       </c>
       <c r="C149">
-        <v>171.33</v>
+        <v>-171.33</v>
       </c>
       <c r="D149" t="s">
         <v>61</v>
@@ -2660,7 +2660,7 @@
         <v>44</v>
       </c>
       <c r="C150">
-        <v>218.15</v>
+        <v>-218.15</v>
       </c>
       <c r="D150" t="s">
         <v>61</v>
@@ -2688,7 +2688,7 @@
         <v>37</v>
       </c>
       <c r="C152">
-        <v>72.81999999999999</v>
+        <v>-72.81999999999999</v>
       </c>
       <c r="D152" t="s">
         <v>60</v>
@@ -2702,7 +2702,7 @@
         <v>40</v>
       </c>
       <c r="C153">
-        <v>201.56</v>
+        <v>-201.56</v>
       </c>
       <c r="D153" t="s">
         <v>58</v>
@@ -2716,7 +2716,7 @@
         <v>39</v>
       </c>
       <c r="C154">
-        <v>199.91</v>
+        <v>-199.91</v>
       </c>
       <c r="D154" t="s">
         <v>56</v>
@@ -2730,7 +2730,7 @@
         <v>34</v>
       </c>
       <c r="C155">
-        <v>726.74</v>
+        <v>-726.74</v>
       </c>
       <c r="D155" t="s">
         <v>56</v>
@@ -2744,7 +2744,7 @@
         <v>39</v>
       </c>
       <c r="C156">
-        <v>800.33</v>
+        <v>-800.33</v>
       </c>
       <c r="D156" t="s">
         <v>56</v>
@@ -2758,7 +2758,7 @@
         <v>41</v>
       </c>
       <c r="C157">
-        <v>32.31</v>
+        <v>-32.31</v>
       </c>
       <c r="D157" t="s">
         <v>60</v>
@@ -2772,7 +2772,7 @@
         <v>38</v>
       </c>
       <c r="C158">
-        <v>378.2</v>
+        <v>-378.2</v>
       </c>
       <c r="D158" t="s">
         <v>61</v>
@@ -2786,7 +2786,7 @@
         <v>48</v>
       </c>
       <c r="C159">
-        <v>79.84999999999999</v>
+        <v>-79.84999999999999</v>
       </c>
       <c r="D159" t="s">
         <v>60</v>
@@ -2800,7 +2800,7 @@
         <v>45</v>
       </c>
       <c r="C160">
-        <v>81.59999999999999</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="D160" t="s">
         <v>58</v>
@@ -2814,7 +2814,7 @@
         <v>37</v>
       </c>
       <c r="C161">
-        <v>64.56</v>
+        <v>-64.56</v>
       </c>
       <c r="D161" t="s">
         <v>60</v>
@@ -2828,7 +2828,7 @@
         <v>52</v>
       </c>
       <c r="C162">
-        <v>70.27</v>
+        <v>-70.27</v>
       </c>
       <c r="D162" t="s">
         <v>62</v>
@@ -2842,7 +2842,7 @@
         <v>34</v>
       </c>
       <c r="C163">
-        <v>325.03</v>
+        <v>-325.03</v>
       </c>
       <c r="D163" t="s">
         <v>56</v>
@@ -2856,7 +2856,7 @@
         <v>37</v>
       </c>
       <c r="C164">
-        <v>86.06</v>
+        <v>-86.06</v>
       </c>
       <c r="D164" t="s">
         <v>60</v>
@@ -2870,7 +2870,7 @@
         <v>36</v>
       </c>
       <c r="C165">
-        <v>97.92</v>
+        <v>-97.92</v>
       </c>
       <c r="D165" t="s">
         <v>59</v>
@@ -2898,7 +2898,7 @@
         <v>41</v>
       </c>
       <c r="C167">
-        <v>111.89</v>
+        <v>-111.89</v>
       </c>
       <c r="D167" t="s">
         <v>60</v>
@@ -2912,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="C168">
-        <v>228.44</v>
+        <v>-228.44</v>
       </c>
       <c r="D168" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>49</v>
       </c>
       <c r="C169">
-        <v>86.59</v>
+        <v>-86.59</v>
       </c>
       <c r="D169" t="s">
         <v>59</v>
@@ -2940,7 +2940,7 @@
         <v>49</v>
       </c>
       <c r="C170">
-        <v>195.15</v>
+        <v>-195.15</v>
       </c>
       <c r="D170" t="s">
         <v>59</v>
@@ -2968,7 +2968,7 @@
         <v>32</v>
       </c>
       <c r="C172">
-        <v>559.49</v>
+        <v>-559.49</v>
       </c>
       <c r="D172" t="s">
         <v>56</v>
@@ -2982,7 +2982,7 @@
         <v>41</v>
       </c>
       <c r="C173">
-        <v>111.39</v>
+        <v>-111.39</v>
       </c>
       <c r="D173" t="s">
         <v>60</v>
@@ -2996,7 +2996,7 @@
         <v>53</v>
       </c>
       <c r="C174">
-        <v>45.91</v>
+        <v>-45.91</v>
       </c>
       <c r="D174" t="s">
         <v>63</v>
@@ -3010,7 +3010,7 @@
         <v>42</v>
       </c>
       <c r="C175">
-        <v>73.81</v>
+        <v>-73.81</v>
       </c>
       <c r="D175" t="s">
         <v>62</v>
@@ -3024,7 +3024,7 @@
         <v>43</v>
       </c>
       <c r="C176">
-        <v>145.77</v>
+        <v>-145.77</v>
       </c>
       <c r="D176" t="s">
         <v>59</v>
@@ -3038,7 +3038,7 @@
         <v>32</v>
       </c>
       <c r="C177">
-        <v>641.86</v>
+        <v>-641.86</v>
       </c>
       <c r="D177" t="s">
         <v>56</v>
@@ -3052,7 +3052,7 @@
         <v>45</v>
       </c>
       <c r="C178">
-        <v>44.03</v>
+        <v>-44.03</v>
       </c>
       <c r="D178" t="s">
         <v>58</v>
@@ -3066,7 +3066,7 @@
         <v>51</v>
       </c>
       <c r="C179">
-        <v>52.41</v>
+        <v>-52.41</v>
       </c>
       <c r="D179" t="s">
         <v>62</v>
@@ -3080,7 +3080,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>151.56</v>
+        <v>-151.56</v>
       </c>
       <c r="D180" t="s">
         <v>61</v>
@@ -3094,7 +3094,7 @@
         <v>44</v>
       </c>
       <c r="C181">
-        <v>417.93</v>
+        <v>-417.93</v>
       </c>
       <c r="D181" t="s">
         <v>61</v>
@@ -3108,7 +3108,7 @@
         <v>55</v>
       </c>
       <c r="C182">
-        <v>11.01</v>
+        <v>-11.01</v>
       </c>
       <c r="D182" t="s">
         <v>61</v>
@@ -3122,7 +3122,7 @@
         <v>47</v>
       </c>
       <c r="C183">
-        <v>48.64</v>
+        <v>-48.64</v>
       </c>
       <c r="D183" t="s">
         <v>63</v>
@@ -3136,7 +3136,7 @@
         <v>52</v>
       </c>
       <c r="C184">
-        <v>30.34</v>
+        <v>-30.34</v>
       </c>
       <c r="D184" t="s">
         <v>62</v>
@@ -3150,7 +3150,7 @@
         <v>39</v>
       </c>
       <c r="C185">
-        <v>19.29</v>
+        <v>-19.29</v>
       </c>
       <c r="D185" t="s">
         <v>56</v>
@@ -3192,7 +3192,7 @@
         <v>32</v>
       </c>
       <c r="C188">
-        <v>365</v>
+        <v>-365</v>
       </c>
       <c r="D188" t="s">
         <v>56</v>
@@ -3206,7 +3206,7 @@
         <v>41</v>
       </c>
       <c r="C189">
-        <v>75.17</v>
+        <v>-75.17</v>
       </c>
       <c r="D189" t="s">
         <v>60</v>
@@ -3220,7 +3220,7 @@
         <v>49</v>
       </c>
       <c r="C190">
-        <v>96.29000000000001</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="D190" t="s">
         <v>59</v>
@@ -3234,7 +3234,7 @@
         <v>39</v>
       </c>
       <c r="C191">
-        <v>838.92</v>
+        <v>-838.92</v>
       </c>
       <c r="D191" t="s">
         <v>56</v>
@@ -3248,7 +3248,7 @@
         <v>36</v>
       </c>
       <c r="C192">
-        <v>43.64</v>
+        <v>-43.64</v>
       </c>
       <c r="D192" t="s">
         <v>59</v>
@@ -3262,7 +3262,7 @@
         <v>39</v>
       </c>
       <c r="C193">
-        <v>160.13</v>
+        <v>-160.13</v>
       </c>
       <c r="D193" t="s">
         <v>56</v>
@@ -3276,7 +3276,7 @@
         <v>52</v>
       </c>
       <c r="C194">
-        <v>96.34999999999999</v>
+        <v>-96.34999999999999</v>
       </c>
       <c r="D194" t="s">
         <v>62</v>
@@ -3290,7 +3290,7 @@
         <v>55</v>
       </c>
       <c r="C195">
-        <v>296.67</v>
+        <v>-296.67</v>
       </c>
       <c r="D195" t="s">
         <v>61</v>
@@ -3304,7 +3304,7 @@
         <v>34</v>
       </c>
       <c r="C196">
-        <v>676.13</v>
+        <v>-676.13</v>
       </c>
       <c r="D196" t="s">
         <v>56</v>
@@ -3332,7 +3332,7 @@
         <v>50</v>
       </c>
       <c r="C198">
-        <v>43.61</v>
+        <v>-43.61</v>
       </c>
       <c r="D198" t="s">
         <v>63</v>
@@ -3346,7 +3346,7 @@
         <v>52</v>
       </c>
       <c r="C199">
-        <v>29.55</v>
+        <v>-29.55</v>
       </c>
       <c r="D199" t="s">
         <v>62</v>
@@ -3360,7 +3360,7 @@
         <v>36</v>
       </c>
       <c r="C200">
-        <v>133.98</v>
+        <v>-133.98</v>
       </c>
       <c r="D200" t="s">
         <v>59</v>
@@ -3374,7 +3374,7 @@
         <v>39</v>
       </c>
       <c r="C201">
-        <v>320.21</v>
+        <v>-320.21</v>
       </c>
       <c r="D201" t="s">
         <v>56</v>
